--- a/outputs/raw_data_cleaning/programmes_import.xlsx
+++ b/outputs/raw_data_cleaning/programmes_import.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="1" r:id="R41b81be5f970480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="1" r:id="Rb67acb244d5a4f55"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/outputs/raw_data_cleaning/programmes_import.xlsx
+++ b/outputs/raw_data_cleaning/programmes_import.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="1" r:id="Rb67acb244d5a4f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="1" r:id="Rf3c9bd687aa047a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,12 +140,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -233,7 +279,7 @@
   <x:cols>
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="33.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -244,7 +290,7 @@
         <x:v>name</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>cluster</x:v>
+        <x:v>years</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -254,8 +300,8 @@
       <x:c r="B2" s="7" t="str">
         <x:v>AAI</x:v>
       </x:c>
-      <x:c r="C2" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C2" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -265,8 +311,8 @@
       <x:c r="B3" s="7" t="str">
         <x:v>ACC</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C3" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -276,8 +322,8 @@
       <x:c r="B4" s="7" t="str">
         <x:v>ASE</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C4" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -287,8 +333,8 @@
       <x:c r="B5" s="7" t="str">
         <x:v>ATM</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C5" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -298,8 +344,8 @@
       <x:c r="B6" s="7" t="str">
         <x:v>BAC</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C6" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -309,9 +355,7 @@
       <x:c r="B7" s="7" t="str">
         <x:v>BCD</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C7" s="7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="7" t="str">
@@ -320,8 +364,8 @@
       <x:c r="B8" s="7" t="str">
         <x:v>BICT</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C8" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -331,9 +375,7 @@
       <x:c r="B9" s="7" t="str">
         <x:v>CBE</x:v>
       </x:c>
-      <x:c r="C9" s="7" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C9" s="7"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="7" t="str">
@@ -342,8 +384,8 @@
       <x:c r="B10" s="7" t="str">
         <x:v>CDM</x:v>
       </x:c>
-      <x:c r="C10" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C10" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -353,8 +395,8 @@
       <x:c r="B11" s="7" t="str">
         <x:v>CEG</x:v>
       </x:c>
-      <x:c r="C11" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C11" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -364,9 +406,7 @@
       <x:c r="B12" s="7" t="str">
         <x:v>CLASIC</x:v>
       </x:c>
-      <x:c r="C12" s="7" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C12" s="7"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="7" t="str">
@@ -375,9 +415,7 @@
       <x:c r="B13" s="7" t="str">
         <x:v>CPC</x:v>
       </x:c>
-      <x:c r="C13" s="7" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C13" s="7"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="7" t="str">
@@ -386,8 +424,8 @@
       <x:c r="B14" s="7" t="str">
         <x:v>CVE</x:v>
       </x:c>
-      <x:c r="C14" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C14" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -397,8 +435,8 @@
       <x:c r="B15" s="7" t="str">
         <x:v>DSC</x:v>
       </x:c>
-      <x:c r="C15" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C15" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -408,8 +446,8 @@
       <x:c r="B16" s="7" t="str">
         <x:v>EDE</x:v>
       </x:c>
-      <x:c r="C16" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C16" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -419,8 +457,8 @@
       <x:c r="B17" s="7" t="str">
         <x:v>EEE</x:v>
       </x:c>
-      <x:c r="C17" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C17" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -430,9 +468,7 @@
       <x:c r="B18" s="7" t="str">
         <x:v>ENG</x:v>
       </x:c>
-      <x:c r="C18" s="7" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C18" s="7"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="7" t="str">
@@ -441,8 +477,8 @@
       <x:c r="B19" s="7" t="str">
         <x:v>EPE</x:v>
       </x:c>
-      <x:c r="C19" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C19" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -452,8 +488,8 @@
       <x:c r="B20" s="7" t="str">
         <x:v>ESE</x:v>
       </x:c>
-      <x:c r="C20" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C20" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -463,9 +499,7 @@
       <x:c r="B21" s="7" t="str">
         <x:v>FCB</x:v>
       </x:c>
-      <x:c r="C21" s="7" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C21" s="7"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="7" t="str">
@@ -474,8 +508,8 @@
       <x:c r="B22" s="7" t="str">
         <x:v>FDT</x:v>
       </x:c>
-      <x:c r="C22" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C22" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -485,9 +519,7 @@
       <x:c r="B23" s="7" t="str">
         <x:v>HSS</x:v>
       </x:c>
-      <x:c r="C23" s="7" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C23" s="7"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="7" t="str">
@@ -496,8 +528,8 @@
       <x:c r="B24" s="7" t="str">
         <x:v>HTM</x:v>
       </x:c>
-      <x:c r="C24" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C24" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -507,8 +539,8 @@
       <x:c r="B25" s="7" t="str">
         <x:v>ICT</x:v>
       </x:c>
-      <x:c r="C25" s="7" t="str">
-        <x:v>Common Modules, Module host key</x:v>
+      <x:c r="C25" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -518,9 +550,7 @@
       <x:c r="B26" s="7" t="str">
         <x:v>IS</x:v>
       </x:c>
-      <x:c r="C26" s="7" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C26" s="7"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="7" t="str">
@@ -529,8 +559,8 @@
       <x:c r="B27" s="7" t="str">
         <x:v>MDME</x:v>
       </x:c>
-      <x:c r="C27" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C27" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -540,8 +570,8 @@
       <x:c r="B28" s="7" t="str">
         <x:v>MEC</x:v>
       </x:c>
-      <x:c r="C28" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C28" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -551,8 +581,8 @@
       <x:c r="B29" s="7" t="str">
         <x:v>METS</x:v>
       </x:c>
-      <x:c r="C29" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C29" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -562,8 +592,8 @@
       <x:c r="B30" s="7" t="str">
         <x:v>NAME</x:v>
       </x:c>
-      <x:c r="C30" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C30" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -573,8 +603,8 @@
       <x:c r="B31" s="7" t="str">
         <x:v>NUR</x:v>
       </x:c>
-      <x:c r="C31" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C31" s="7" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -584,9 +614,7 @@
       <x:c r="B32" s="7" t="str">
         <x:v>POST</x:v>
       </x:c>
-      <x:c r="C32" s="7" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C32" s="7"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="7" t="str">
@@ -595,9 +623,7 @@
       <x:c r="B33" s="7" t="str">
         <x:v>PRE</x:v>
       </x:c>
-      <x:c r="C33" s="7" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C33" s="7"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="7" t="str">
@@ -606,8 +632,8 @@
       <x:c r="B34" s="7" t="str">
         <x:v>RSE</x:v>
       </x:c>
-      <x:c r="C34" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C34" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -617,8 +643,8 @@
       <x:c r="B35" s="7" t="str">
         <x:v>RTY</x:v>
       </x:c>
-      <x:c r="C35" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C35" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -628,8 +654,8 @@
       <x:c r="B36" s="7" t="str">
         <x:v>SBE</x:v>
       </x:c>
-      <x:c r="C36" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C36" s="7" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -639,9 +665,7 @@
       <x:c r="B37" s="7" t="str">
         <x:v>SE</x:v>
       </x:c>
-      <x:c r="C37" s="7" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C37" s="7"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="7" t="str">
@@ -650,8 +674,8 @@
       <x:c r="B38" s="7" t="str">
         <x:v>SLT</x:v>
       </x:c>
-      <x:c r="C38" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C38" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -661,8 +685,8 @@
       <x:c r="B39" s="7" t="str">
         <x:v>TCE</x:v>
       </x:c>
-      <x:c r="C39" s="7" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C39" s="7" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -672,9 +696,7 @@
       <x:c r="B40" s="7" t="str">
         <x:v>TITO</x:v>
       </x:c>
-      <x:c r="C40" s="7" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C40" s="7"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
